--- a/input/event20201213_QAQC_CB_FEB2021.xlsx
+++ b/input/event20201213_QAQC_CB_FEB2021.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10212"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christine bentley\Desktop\Deer Data 2017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robynirvine/Analyses/llgaay-gwii-20/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F60C81-A6B9-6C47-8D13-FC87503A791E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46656" yWindow="9660" windowWidth="27636" windowHeight="16944"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="35840" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -23,12 +24,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Christine Bentley</author>
   </authors>
   <commentList>
-    <comment ref="B498" authorId="0" shapeId="0">
+    <comment ref="B498" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -52,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B499" authorId="0" shapeId="0">
+    <comment ref="B499" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -2741,7 +2742,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -3651,30 +3652,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P606"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.69921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.796875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.8984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.59765625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.09765625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="197.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.19921875" style="1"/>
+    <col min="17" max="16384" width="11.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>799</v>
       </c>
@@ -3724,7 +3726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>801</v>
       </c>
@@ -3771,7 +3773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>801</v>
       </c>
@@ -3818,7 +3820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>801</v>
       </c>
@@ -3865,7 +3867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>827</v>
       </c>
@@ -3912,7 +3914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>801</v>
       </c>
@@ -3959,7 +3961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>801</v>
       </c>
@@ -4006,7 +4008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>801</v>
       </c>
@@ -4053,7 +4055,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>801</v>
       </c>
@@ -4100,7 +4102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>801</v>
       </c>
@@ -4147,7 +4149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>801</v>
       </c>
@@ -4194,7 +4196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>801</v>
       </c>
@@ -4241,7 +4243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>801</v>
       </c>
@@ -4288,7 +4290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>807</v>
       </c>
@@ -4338,7 +4340,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>801</v>
       </c>
@@ -4385,7 +4387,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>801</v>
       </c>
@@ -4432,7 +4434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>801</v>
       </c>
@@ -4479,7 +4481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>807</v>
       </c>
@@ -4529,7 +4531,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>801</v>
       </c>
@@ -4576,7 +4578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>801</v>
       </c>
@@ -4623,7 +4625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>801</v>
       </c>
@@ -4670,7 +4672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>801</v>
       </c>
@@ -4717,7 +4719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>801</v>
       </c>
@@ -4764,7 +4766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>827</v>
       </c>
@@ -4811,7 +4813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>801</v>
       </c>
@@ -4858,7 +4860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>801</v>
       </c>
@@ -4905,7 +4907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>801</v>
       </c>
@@ -4952,7 +4954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>801</v>
       </c>
@@ -4999,7 +5001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>801</v>
       </c>
@@ -5046,7 +5048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>801</v>
       </c>
@@ -5093,7 +5095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>801</v>
       </c>
@@ -5140,7 +5142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>801</v>
       </c>
@@ -5187,7 +5189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>801</v>
       </c>
@@ -5234,7 +5236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>801</v>
       </c>
@@ -5281,7 +5283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>801</v>
       </c>
@@ -5328,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>801</v>
       </c>
@@ -5375,7 +5377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>827</v>
       </c>
@@ -5422,7 +5424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>801</v>
       </c>
@@ -5469,7 +5471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>801</v>
       </c>
@@ -5516,7 +5518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>801</v>
       </c>
@@ -5563,7 +5565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>801</v>
       </c>
@@ -5610,7 +5612,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>807</v>
       </c>
@@ -5660,7 +5662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>807</v>
       </c>
@@ -5710,7 +5712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>801</v>
       </c>
@@ -5757,7 +5759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>801</v>
       </c>
@@ -5804,7 +5806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>801</v>
       </c>
@@ -5851,7 +5853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>801</v>
       </c>
@@ -5898,7 +5900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>801</v>
       </c>
@@ -5945,7 +5947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>801</v>
       </c>
@@ -5992,7 +5994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>801</v>
       </c>
@@ -6039,7 +6041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>827</v>
       </c>
@@ -6086,7 +6088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>807</v>
       </c>
@@ -6136,7 +6138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>801</v>
       </c>
@@ -6183,7 +6185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>801</v>
       </c>
@@ -6230,7 +6232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>801</v>
       </c>
@@ -6277,7 +6279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>802</v>
       </c>
@@ -6327,7 +6329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>801</v>
       </c>
@@ -6374,7 +6376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>801</v>
       </c>
@@ -6421,7 +6423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>801</v>
       </c>
@@ -6468,7 +6470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>801</v>
       </c>
@@ -6515,7 +6517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>801</v>
       </c>
@@ -6562,7 +6564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>801</v>
       </c>
@@ -6609,7 +6611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>801</v>
       </c>
@@ -6656,7 +6658,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>801</v>
       </c>
@@ -6703,7 +6705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>801</v>
       </c>
@@ -6750,7 +6752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>807</v>
       </c>
@@ -6800,7 +6802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>807</v>
       </c>
@@ -6850,7 +6852,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>801</v>
       </c>
@@ -6897,7 +6899,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>801</v>
       </c>
@@ -6944,7 +6946,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>801</v>
       </c>
@@ -6991,7 +6993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>801</v>
       </c>
@@ -7038,7 +7040,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="72" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>801</v>
       </c>
@@ -7085,7 +7087,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="73" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>801</v>
       </c>
@@ -7132,7 +7134,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>801</v>
       </c>
@@ -7179,7 +7181,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>801</v>
       </c>
@@ -7226,7 +7228,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>807</v>
       </c>
@@ -7276,7 +7278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>801</v>
       </c>
@@ -7323,7 +7325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>801</v>
       </c>
@@ -7370,7 +7372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>801</v>
       </c>
@@ -7417,7 +7419,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>801</v>
       </c>
@@ -7464,7 +7466,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>807</v>
       </c>
@@ -7514,7 +7516,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>801</v>
       </c>
@@ -7561,7 +7563,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="83" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>807</v>
       </c>
@@ -7611,7 +7613,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>801</v>
       </c>
@@ -7658,7 +7660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>801</v>
       </c>
@@ -7705,7 +7707,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>801</v>
       </c>
@@ -7752,7 +7754,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>801</v>
       </c>
@@ -7799,7 +7801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>801</v>
       </c>
@@ -7846,7 +7848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>801</v>
       </c>
@@ -7893,7 +7895,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>801</v>
       </c>
@@ -7940,7 +7942,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>801</v>
       </c>
@@ -7987,7 +7989,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>801</v>
       </c>
@@ -8034,7 +8036,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>801</v>
       </c>
@@ -8081,7 +8083,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="94" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>801</v>
       </c>
@@ -8128,7 +8130,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="95" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>801</v>
       </c>
@@ -8175,7 +8177,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>801</v>
       </c>
@@ -8225,7 +8227,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="97" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>801</v>
       </c>
@@ -8272,7 +8274,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>802</v>
       </c>
@@ -8322,7 +8324,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>801</v>
       </c>
@@ -8369,7 +8371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>801</v>
       </c>
@@ -8416,7 +8418,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>801</v>
       </c>
@@ -8463,7 +8465,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>801</v>
       </c>
@@ -8510,7 +8512,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="103" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>801</v>
       </c>
@@ -8557,7 +8559,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="104" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>801</v>
       </c>
@@ -8604,7 +8606,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>801</v>
       </c>
@@ -8651,7 +8653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>801</v>
       </c>
@@ -8698,7 +8700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>801</v>
       </c>
@@ -8745,7 +8747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>801</v>
       </c>
@@ -8792,7 +8794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>802</v>
       </c>
@@ -8842,7 +8844,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="110" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>801</v>
       </c>
@@ -8889,7 +8891,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="111" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>807</v>
       </c>
@@ -8939,7 +8941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>801</v>
       </c>
@@ -8986,7 +8988,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="113" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>823</v>
       </c>
@@ -9033,7 +9035,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="114" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>801</v>
       </c>
@@ -9080,7 +9082,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="115" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>801</v>
       </c>
@@ -9127,7 +9129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>827</v>
       </c>
@@ -9174,7 +9176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>801</v>
       </c>
@@ -9221,7 +9223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>801</v>
       </c>
@@ -9268,7 +9270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>801</v>
       </c>
@@ -9315,7 +9317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>801</v>
       </c>
@@ -9362,7 +9364,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>801</v>
       </c>
@@ -9409,7 +9411,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>801</v>
       </c>
@@ -9456,7 +9458,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="123" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>801</v>
       </c>
@@ -9503,7 +9505,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>827</v>
       </c>
@@ -9550,7 +9552,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>807</v>
       </c>
@@ -9600,7 +9602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>801</v>
       </c>
@@ -9647,7 +9649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>801</v>
       </c>
@@ -9694,7 +9696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>801</v>
       </c>
@@ -9741,7 +9743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>801</v>
       </c>
@@ -9788,7 +9790,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>801</v>
       </c>
@@ -9835,7 +9837,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="131" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>827</v>
       </c>
@@ -9882,7 +9884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>801</v>
       </c>
@@ -9929,7 +9931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>802</v>
       </c>
@@ -9979,7 +9981,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="134" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>801</v>
       </c>
@@ -10026,7 +10028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>827</v>
       </c>
@@ -10073,7 +10075,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="136" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>801</v>
       </c>
@@ -10120,7 +10122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>801</v>
       </c>
@@ -10167,7 +10169,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>807</v>
       </c>
@@ -10217,7 +10219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>801</v>
       </c>
@@ -10264,7 +10266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>801</v>
       </c>
@@ -10311,7 +10313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>827</v>
       </c>
@@ -10358,7 +10360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>801</v>
       </c>
@@ -10405,7 +10407,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>801</v>
       </c>
@@ -10452,7 +10454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>801</v>
       </c>
@@ -10499,7 +10501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>807</v>
       </c>
@@ -10549,7 +10551,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>801</v>
       </c>
@@ -10596,7 +10598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>801</v>
       </c>
@@ -10643,7 +10645,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="148" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>802</v>
       </c>
@@ -10693,7 +10695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>807</v>
       </c>
@@ -10743,7 +10745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>807</v>
       </c>
@@ -10793,7 +10795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>801</v>
       </c>
@@ -10840,7 +10842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>801</v>
       </c>
@@ -10887,7 +10889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>801</v>
       </c>
@@ -10934,7 +10936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>801</v>
       </c>
@@ -10981,7 +10983,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="155" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>801</v>
       </c>
@@ -11028,7 +11030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>801</v>
       </c>
@@ -11075,7 +11077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>801</v>
       </c>
@@ -11122,7 +11124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>827</v>
       </c>
@@ -11169,7 +11171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>801</v>
       </c>
@@ -11216,7 +11218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>801</v>
       </c>
@@ -11263,7 +11265,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>801</v>
       </c>
@@ -11310,7 +11312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>802</v>
       </c>
@@ -11360,7 +11362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>801</v>
       </c>
@@ -11407,7 +11409,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="164" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>801</v>
       </c>
@@ -11454,7 +11456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>801</v>
       </c>
@@ -11501,7 +11503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>801</v>
       </c>
@@ -11548,7 +11550,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="167" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>801</v>
       </c>
@@ -11595,7 +11597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>801</v>
       </c>
@@ -11642,7 +11644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:16" s="2" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" s="2" customFormat="1" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>801</v>
       </c>
@@ -11689,7 +11691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>801</v>
       </c>
@@ -11736,7 +11738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>801</v>
       </c>
@@ -11783,7 +11785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>801</v>
       </c>
@@ -11830,7 +11832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>801</v>
       </c>
@@ -11877,7 +11879,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="174" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>801</v>
       </c>
@@ -11924,7 +11926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>801</v>
       </c>
@@ -11971,7 +11973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>801</v>
       </c>
@@ -12018,7 +12020,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>801</v>
       </c>
@@ -12065,7 +12067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>801</v>
       </c>
@@ -12112,7 +12114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>801</v>
       </c>
@@ -12159,7 +12161,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="180" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>801</v>
       </c>
@@ -12206,7 +12208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>801</v>
       </c>
@@ -12253,7 +12255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>801</v>
       </c>
@@ -12300,7 +12302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>801</v>
       </c>
@@ -12347,7 +12349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>801</v>
       </c>
@@ -12394,7 +12396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>801</v>
       </c>
@@ -12441,7 +12443,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="186" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>801</v>
       </c>
@@ -12488,7 +12490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>801</v>
       </c>
@@ -12535,7 +12537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>801</v>
       </c>
@@ -12582,7 +12584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>801</v>
       </c>
@@ -12629,7 +12631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>802</v>
       </c>
@@ -12679,7 +12681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>827</v>
       </c>
@@ -12726,7 +12728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>801</v>
       </c>
@@ -12773,7 +12775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>801</v>
       </c>
@@ -12820,7 +12822,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="194" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>801</v>
       </c>
@@ -12867,7 +12869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>801</v>
       </c>
@@ -12914,7 +12916,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>801</v>
       </c>
@@ -12961,7 +12963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>801</v>
       </c>
@@ -13008,7 +13010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>801</v>
       </c>
@@ -13055,7 +13057,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>801</v>
       </c>
@@ -13102,7 +13104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>801</v>
       </c>
@@ -13149,7 +13151,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>801</v>
       </c>
@@ -13196,7 +13198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>801</v>
       </c>
@@ -13243,7 +13245,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="203" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>801</v>
       </c>
@@ -13290,7 +13292,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="204" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>801</v>
       </c>
@@ -13337,7 +13339,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="205" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>801</v>
       </c>
@@ -13384,7 +13386,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="206" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>801</v>
       </c>
@@ -13431,7 +13433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>801</v>
       </c>
@@ -13478,7 +13480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>801</v>
       </c>
@@ -13525,7 +13527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>801</v>
       </c>
@@ -13572,7 +13574,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>801</v>
       </c>
@@ -13619,7 +13621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>801</v>
       </c>
@@ -13666,7 +13668,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="212" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>801</v>
       </c>
@@ -13713,7 +13715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>801</v>
       </c>
@@ -13760,7 +13762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>801</v>
       </c>
@@ -13807,7 +13809,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>801</v>
       </c>
@@ -13854,7 +13856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>801</v>
       </c>
@@ -13901,7 +13903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>801</v>
       </c>
@@ -13948,7 +13950,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="218" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>801</v>
       </c>
@@ -13995,7 +13997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>827</v>
       </c>
@@ -14042,7 +14044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>801</v>
       </c>
@@ -14089,7 +14091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>801</v>
       </c>
@@ -14136,7 +14138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>801</v>
       </c>
@@ -14183,7 +14185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>801</v>
       </c>
@@ -14230,7 +14232,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="224" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>801</v>
       </c>
@@ -14277,7 +14279,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="225" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>801</v>
       </c>
@@ -14324,7 +14326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>801</v>
       </c>
@@ -14371,7 +14373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>801</v>
       </c>
@@ -14418,7 +14420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>807</v>
       </c>
@@ -14468,7 +14470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>807</v>
       </c>
@@ -14518,7 +14520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>801</v>
       </c>
@@ -14565,7 +14567,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="231" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>801</v>
       </c>
@@ -14612,7 +14614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>801</v>
       </c>
@@ -14659,7 +14661,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="233" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>801</v>
       </c>
@@ -14706,7 +14708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>801</v>
       </c>
@@ -14753,7 +14755,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>807</v>
       </c>
@@ -14803,7 +14805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>802</v>
       </c>
@@ -14853,7 +14855,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="237" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>801</v>
       </c>
@@ -14900,7 +14902,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="238" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>801</v>
       </c>
@@ -14947,7 +14949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>801</v>
       </c>
@@ -14994,7 +14996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>827</v>
       </c>
@@ -15041,7 +15043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>827</v>
       </c>
@@ -15088,7 +15090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>801</v>
       </c>
@@ -15135,7 +15137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>807</v>
       </c>
@@ -15185,7 +15187,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="244" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>801</v>
       </c>
@@ -15232,7 +15234,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="245" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>801</v>
       </c>
@@ -15279,7 +15281,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="246" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>807</v>
       </c>
@@ -15329,7 +15331,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="247" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>801</v>
       </c>
@@ -15376,7 +15378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>801</v>
       </c>
@@ -15423,7 +15425,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>801</v>
       </c>
@@ -15470,7 +15472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>801</v>
       </c>
@@ -15517,7 +15519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="251" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>801</v>
       </c>
@@ -15564,7 +15566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>801</v>
       </c>
@@ -15611,7 +15613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>801</v>
       </c>
@@ -15658,7 +15660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>801</v>
       </c>
@@ -15705,7 +15707,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="255" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>801</v>
       </c>
@@ -15752,7 +15754,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="256" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>801</v>
       </c>
@@ -15799,7 +15801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="257" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>801</v>
       </c>
@@ -15846,7 +15848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>801</v>
       </c>
@@ -15893,7 +15895,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>801</v>
       </c>
@@ -15940,7 +15942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="260" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>801</v>
       </c>
@@ -15987,7 +15989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>801</v>
       </c>
@@ -16034,7 +16036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>801</v>
       </c>
@@ -16081,7 +16083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>801</v>
       </c>
@@ -16128,7 +16130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>801</v>
       </c>
@@ -16175,7 +16177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="265" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>801</v>
       </c>
@@ -16222,7 +16224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>801</v>
       </c>
@@ -16269,7 +16271,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="267" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>801</v>
       </c>
@@ -16316,7 +16318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>801</v>
       </c>
@@ -16363,7 +16365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>827</v>
       </c>
@@ -16410,7 +16412,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>801</v>
       </c>
@@ -16457,7 +16459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>801</v>
       </c>
@@ -16504,7 +16506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>801</v>
       </c>
@@ -16551,7 +16553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>801</v>
       </c>
@@ -16598,7 +16600,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="274" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>801</v>
       </c>
@@ -16645,7 +16647,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="275" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>801</v>
       </c>
@@ -16692,7 +16694,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>801</v>
       </c>
@@ -16739,7 +16741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>801</v>
       </c>
@@ -16786,7 +16788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>801</v>
       </c>
@@ -16833,7 +16835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>801</v>
       </c>
@@ -16880,7 +16882,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>801</v>
       </c>
@@ -16927,7 +16929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>801</v>
       </c>
@@ -16974,7 +16976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="282" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>802</v>
       </c>
@@ -17024,7 +17026,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="283" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>802</v>
       </c>
@@ -17074,7 +17076,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="284" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>802</v>
       </c>
@@ -17124,7 +17126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:16" s="2" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:16" s="2" customFormat="1" ht="16.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
         <v>801</v>
       </c>
@@ -17171,7 +17173,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="286" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
         <v>827</v>
       </c>
@@ -17218,7 +17220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>827</v>
       </c>
@@ -17265,7 +17267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
         <v>827</v>
       </c>
@@ -17312,7 +17314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
         <v>827</v>
       </c>
@@ -17359,7 +17361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
         <v>827</v>
       </c>
@@ -17406,7 +17408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
         <v>827</v>
       </c>
@@ -17453,7 +17455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>827</v>
       </c>
@@ -17500,7 +17502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>827</v>
       </c>
@@ -17547,7 +17549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>827</v>
       </c>
@@ -17594,7 +17596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
         <v>801</v>
       </c>
@@ -17641,7 +17643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>801</v>
       </c>
@@ -17688,7 +17690,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="297" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>801</v>
       </c>
@@ -17735,7 +17737,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="298" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
         <v>801</v>
       </c>
@@ -17782,7 +17784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="299" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
         <v>801</v>
       </c>
@@ -17829,7 +17831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="300" spans="1:16" s="2" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:16" s="2" customFormat="1" ht="16.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
         <v>802</v>
       </c>
@@ -17879,7 +17881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
         <v>801</v>
       </c>
@@ -17926,7 +17928,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="302" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>801</v>
       </c>
@@ -17973,7 +17975,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="303" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
         <v>801</v>
       </c>
@@ -18020,7 +18022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
         <v>801</v>
       </c>
@@ -18067,7 +18069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
         <v>801</v>
       </c>
@@ -18114,7 +18116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
         <v>807</v>
       </c>
@@ -18164,7 +18166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>801</v>
       </c>
@@ -18211,7 +18213,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="308" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
         <v>801</v>
       </c>
@@ -18258,7 +18260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>802</v>
       </c>
@@ -18308,7 +18310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>801</v>
       </c>
@@ -18355,7 +18357,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>801</v>
       </c>
@@ -18402,7 +18404,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="312" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>801</v>
       </c>
@@ -18449,7 +18451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
         <v>807</v>
       </c>
@@ -18499,7 +18501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="314" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
         <v>801</v>
       </c>
@@ -18546,7 +18548,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="315" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
         <v>801</v>
       </c>
@@ -18593,7 +18595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
         <v>827</v>
       </c>
@@ -18640,7 +18642,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="317" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
         <v>827</v>
       </c>
@@ -18687,7 +18689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="318" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
         <v>827</v>
       </c>
@@ -18734,7 +18736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
         <v>827</v>
       </c>
@@ -18781,7 +18783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
         <v>827</v>
       </c>
@@ -18828,7 +18830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="321" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
         <v>801</v>
       </c>
@@ -18875,7 +18877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
         <v>801</v>
       </c>
@@ -18922,7 +18924,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="323" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
         <v>801</v>
       </c>
@@ -18969,7 +18971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="324" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
         <v>801</v>
       </c>
@@ -19016,7 +19018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
         <v>801</v>
       </c>
@@ -19063,7 +19065,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="326" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
         <v>801</v>
       </c>
@@ -19110,7 +19112,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="327" spans="1:16" s="2" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:16" s="2" customFormat="1" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
         <v>801</v>
       </c>
@@ -19157,7 +19159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
         <v>801</v>
       </c>
@@ -19204,7 +19206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="329" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
         <v>801</v>
       </c>
@@ -19251,7 +19253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
         <v>802</v>
       </c>
@@ -19301,7 +19303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
         <v>802</v>
       </c>
@@ -19351,7 +19353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
         <v>807</v>
       </c>
@@ -19401,7 +19403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="333" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
         <v>807</v>
       </c>
@@ -19451,7 +19453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
         <v>801</v>
       </c>
@@ -19498,7 +19500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
         <v>801</v>
       </c>
@@ -19545,7 +19547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
         <v>827</v>
       </c>
@@ -19592,7 +19594,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="337" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
         <v>807</v>
       </c>
@@ -19642,7 +19644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="338" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
         <v>827</v>
       </c>
@@ -19689,7 +19691,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="339" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
         <v>801</v>
       </c>
@@ -19736,7 +19738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
         <v>801</v>
       </c>
@@ -19783,7 +19785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="341" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
         <v>801</v>
       </c>
@@ -19830,7 +19832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="342" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
         <v>801</v>
       </c>
@@ -19877,7 +19879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="343" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
         <v>801</v>
       </c>
@@ -19924,7 +19926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="344" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
         <v>827</v>
       </c>
@@ -19971,7 +19973,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="345" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
         <v>801</v>
       </c>
@@ -20018,7 +20020,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="346" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
         <v>801</v>
       </c>
@@ -20065,7 +20067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="347" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
         <v>801</v>
       </c>
@@ -20112,7 +20114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
         <v>801</v>
       </c>
@@ -20159,7 +20161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
         <v>801</v>
       </c>
@@ -20206,7 +20208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="350" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
         <v>801</v>
       </c>
@@ -20253,7 +20255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
         <v>801</v>
       </c>
@@ -20300,7 +20302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="352" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
         <v>801</v>
       </c>
@@ -20347,7 +20349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="353" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
         <v>801</v>
       </c>
@@ -20394,7 +20396,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="354" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
         <v>801</v>
       </c>
@@ -20441,7 +20443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
         <v>801</v>
       </c>
@@ -20488,7 +20490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="356" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2" t="s">
         <v>801</v>
       </c>
@@ -20535,7 +20537,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="357" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
         <v>802</v>
       </c>
@@ -20585,7 +20587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
         <v>802</v>
       </c>
@@ -20635,7 +20637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="359" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
         <v>807</v>
       </c>
@@ -20685,7 +20687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="360" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
         <v>801</v>
       </c>
@@ -20732,7 +20734,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="361" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
         <v>801</v>
       </c>
@@ -20779,7 +20781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
         <v>801</v>
       </c>
@@ -20826,7 +20828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
         <v>801</v>
       </c>
@@ -20873,7 +20875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
         <v>801</v>
       </c>
@@ -20920,7 +20922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="365" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
         <v>801</v>
       </c>
@@ -20967,7 +20969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
         <v>807</v>
       </c>
@@ -21017,7 +21019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="367" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
         <v>827</v>
       </c>
@@ -21064,7 +21066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="368" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
         <v>801</v>
       </c>
@@ -21111,7 +21113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="369" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
         <v>801</v>
       </c>
@@ -21158,7 +21160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
         <v>801</v>
       </c>
@@ -21205,7 +21207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
         <v>801</v>
       </c>
@@ -21252,7 +21254,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="372" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2" t="s">
         <v>807</v>
       </c>
@@ -21302,7 +21304,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="373" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
         <v>801</v>
       </c>
@@ -21349,7 +21351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
         <v>801</v>
       </c>
@@ -21396,7 +21398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="375" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
         <v>807</v>
       </c>
@@ -21422,7 +21424,7 @@
         <v>42907.875</v>
       </c>
       <c r="I375" s="3">
-        <v>42907.048611111109</v>
+        <v>42908.048611111109</v>
       </c>
       <c r="J375" s="2">
         <v>0</v>
@@ -21446,7 +21448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
         <v>801</v>
       </c>
@@ -21493,7 +21495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="377" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2" t="s">
         <v>801</v>
       </c>
@@ -21540,7 +21542,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="378" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
         <v>801</v>
       </c>
@@ -21587,7 +21589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="379" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2" t="s">
         <v>807</v>
       </c>
@@ -21637,7 +21639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="380" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2" t="s">
         <v>801</v>
       </c>
@@ -21684,7 +21686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="381" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2" t="s">
         <v>801</v>
       </c>
@@ -21731,7 +21733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="382" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2" t="s">
         <v>801</v>
       </c>
@@ -21778,7 +21780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
         <v>801</v>
       </c>
@@ -21825,7 +21827,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="384" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2" t="s">
         <v>801</v>
       </c>
@@ -21872,7 +21874,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="385" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2" t="s">
         <v>801</v>
       </c>
@@ -21919,7 +21921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="386" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2" t="s">
         <v>807</v>
       </c>
@@ -21969,7 +21971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="387" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2" t="s">
         <v>801</v>
       </c>
@@ -22016,7 +22018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="388" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
         <v>801</v>
       </c>
@@ -22063,7 +22065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="389" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2" t="s">
         <v>801</v>
       </c>
@@ -22110,7 +22112,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="390" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2" t="s">
         <v>827</v>
       </c>
@@ -22157,7 +22159,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="391" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2" t="s">
         <v>827</v>
       </c>
@@ -22204,7 +22206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="392" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2" t="s">
         <v>827</v>
       </c>
@@ -22251,7 +22253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="393" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
         <v>801</v>
       </c>
@@ -22298,7 +22300,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="394" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2" t="s">
         <v>827</v>
       </c>
@@ -22345,7 +22347,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="395" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
         <v>801</v>
       </c>
@@ -22392,7 +22394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="396" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2" t="s">
         <v>802</v>
       </c>
@@ -22442,7 +22444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="397" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
         <v>801</v>
       </c>
@@ -22489,7 +22491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="398" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
         <v>801</v>
       </c>
@@ -22536,7 +22538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="399" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2" t="s">
         <v>801</v>
       </c>
@@ -22583,7 +22585,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="400" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
         <v>801</v>
       </c>
@@ -22630,7 +22632,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="401" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
         <v>801</v>
       </c>
@@ -22677,7 +22679,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="402" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
         <v>801</v>
       </c>
@@ -22724,7 +22726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
         <v>801</v>
       </c>
@@ -22771,7 +22773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="404" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2" t="s">
         <v>801</v>
       </c>
@@ -22818,7 +22820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="405" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
         <v>801</v>
       </c>
@@ -22865,7 +22867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2" t="s">
         <v>801</v>
       </c>
@@ -22912,7 +22914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="407" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2" t="s">
         <v>801</v>
       </c>
@@ -22959,7 +22961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="408" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2" t="s">
         <v>801</v>
       </c>
@@ -23006,7 +23008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="409" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2" t="s">
         <v>801</v>
       </c>
@@ -23053,7 +23055,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="410" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="2" t="s">
         <v>802</v>
       </c>
@@ -23103,7 +23105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="411" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
         <v>801</v>
       </c>
@@ -23150,7 +23152,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="412" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
         <v>801</v>
       </c>
@@ -23197,7 +23199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="413" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
         <v>801</v>
       </c>
@@ -23244,7 +23246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
         <v>801</v>
       </c>
@@ -23291,7 +23293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="415" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
         <v>801</v>
       </c>
@@ -23338,7 +23340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="416" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2" t="s">
         <v>801</v>
       </c>
@@ -23385,7 +23387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="417" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
         <v>801</v>
       </c>
@@ -23432,7 +23434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
         <v>801</v>
       </c>
@@ -23479,7 +23481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="419" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2" t="s">
         <v>801</v>
       </c>
@@ -23526,7 +23528,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="420" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2" t="s">
         <v>801</v>
       </c>
@@ -23573,7 +23575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="421" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2" t="s">
         <v>801</v>
       </c>
@@ -23620,7 +23622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="422" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2" t="s">
         <v>801</v>
       </c>
@@ -23667,7 +23669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
         <v>802</v>
       </c>
@@ -23717,7 +23719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="424" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2" t="s">
         <v>801</v>
       </c>
@@ -23764,7 +23766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
         <v>807</v>
       </c>
@@ -23814,7 +23816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="426" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2" t="s">
         <v>801</v>
       </c>
@@ -23861,7 +23863,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="427" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
         <v>801</v>
       </c>
@@ -23908,7 +23910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
         <v>801</v>
       </c>
@@ -23955,7 +23957,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="429" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
         <v>801</v>
       </c>
@@ -24002,7 +24004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="430" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
         <v>801</v>
       </c>
@@ -24049,7 +24051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="431" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
         <v>801</v>
       </c>
@@ -24096,7 +24098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="432" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
         <v>802</v>
       </c>
@@ -24146,7 +24148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="433" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
         <v>802</v>
       </c>
@@ -24196,7 +24198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="434" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2" t="s">
         <v>801</v>
       </c>
@@ -24243,7 +24245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="435" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
         <v>801</v>
       </c>
@@ -24290,7 +24292,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="436" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
         <v>801</v>
       </c>
@@ -24337,7 +24339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="437" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
         <v>802</v>
       </c>
@@ -24387,7 +24389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="438" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
         <v>801</v>
       </c>
@@ -24434,7 +24436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="439" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:16" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
         <v>827</v>
       </c>
@@ -24481,7 +24483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="440" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
         <v>827</v>
       </c>
@@ -24528,7 +24530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="441" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
         <v>827</v>
       </c>
@@ -24575,7 +24577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="442" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
         <v>827</v>
       </c>
@@ -24622,7 +24624,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="443" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
         <v>801</v>
       </c>
@@ -24669,7 +24671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
         <v>801</v>
       </c>
@@ -24716,7 +24718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="445" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
         <v>801</v>
       </c>
@@ -24763,7 +24765,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="446" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
         <v>801</v>
       </c>
@@ -24810,7 +24812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="447" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
         <v>807</v>
       </c>
@@ -24860,7 +24862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="448" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2" t="s">
         <v>807</v>
       </c>
@@ -24910,7 +24912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="449" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
         <v>801</v>
       </c>
@@ -24957,7 +24959,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="450" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
         <v>801</v>
       </c>
@@ -25004,7 +25006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
         <v>807</v>
       </c>
@@ -25054,7 +25056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="452" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
         <v>801</v>
       </c>
@@ -25101,7 +25103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
         <v>801</v>
       </c>
@@ -25148,7 +25150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="454" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2" t="s">
         <v>801</v>
       </c>
@@ -25195,7 +25197,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="455" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
         <v>801</v>
       </c>
@@ -25242,7 +25244,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2" t="s">
         <v>801</v>
       </c>
@@ -25289,7 +25291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
         <v>801</v>
       </c>
@@ -25336,7 +25338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="458" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
         <v>801</v>
       </c>
@@ -25383,7 +25385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="459" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
         <v>801</v>
       </c>
@@ -25430,7 +25432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">
         <v>801</v>
       </c>
@@ -25477,7 +25479,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="461" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
         <v>801</v>
       </c>
@@ -25524,7 +25526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="462" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="2" t="s">
         <v>801</v>
       </c>
@@ -25571,7 +25573,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="463" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
         <v>807</v>
       </c>
@@ -25621,7 +25623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="464" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
         <v>802</v>
       </c>
@@ -25671,7 +25673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="465" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
         <v>801</v>
       </c>
@@ -25718,7 +25720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
         <v>801</v>
       </c>
@@ -25765,7 +25767,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
         <v>801</v>
       </c>
@@ -25812,7 +25814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
         <v>801</v>
       </c>
@@ -25859,7 +25861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>801</v>
       </c>
@@ -25906,7 +25908,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="470" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2" t="s">
         <v>801</v>
       </c>
@@ -25953,7 +25955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="471" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
         <v>801</v>
       </c>
@@ -26000,7 +26002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="472" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
         <v>801</v>
       </c>
@@ -26047,7 +26049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="473" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
         <v>820</v>
       </c>
@@ -26097,7 +26099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
         <v>801</v>
       </c>
@@ -26144,7 +26146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="475" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
         <v>801</v>
       </c>
@@ -26191,7 +26193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="476" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
         <v>801</v>
       </c>
@@ -26238,7 +26240,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="477" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
         <v>807</v>
       </c>
@@ -26288,7 +26290,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="478" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
         <v>807</v>
       </c>
@@ -26338,7 +26340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2" t="s">
         <v>801</v>
       </c>
@@ -26385,7 +26387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
         <v>801</v>
       </c>
@@ -26432,7 +26434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="481" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
         <v>801</v>
       </c>
@@ -26479,7 +26481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="482" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
         <v>801</v>
       </c>
@@ -26526,7 +26528,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="483" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
         <v>801</v>
       </c>
@@ -26573,7 +26575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="484" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
         <v>801</v>
       </c>
@@ -26620,7 +26622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:16" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
         <v>801</v>
       </c>
@@ -26667,7 +26669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="486" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
         <v>801</v>
       </c>
@@ -26714,7 +26716,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="487" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
         <v>801</v>
       </c>
@@ -26761,7 +26763,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="488" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
         <v>801</v>
       </c>
@@ -26808,7 +26810,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="489" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
         <v>801</v>
       </c>
@@ -26855,7 +26857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="490" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
         <v>801</v>
       </c>
@@ -26902,7 +26904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
         <v>801</v>
       </c>
@@ -26949,7 +26951,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="492" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
         <v>801</v>
       </c>
@@ -26996,7 +26998,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="493" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
         <v>801</v>
       </c>
@@ -27043,7 +27045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="494" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
         <v>807</v>
       </c>
@@ -27093,7 +27095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="495" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
         <v>801</v>
       </c>
@@ -27140,7 +27142,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="496" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
         <v>807</v>
       </c>
@@ -27190,7 +27192,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="497" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
         <v>801</v>
       </c>
@@ -27237,7 +27239,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="498" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="5" t="s">
         <v>807</v>
       </c>
@@ -27287,7 +27289,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="499" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="5" t="s">
         <v>807</v>
       </c>
@@ -27337,7 +27339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="500" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
         <v>801</v>
       </c>
@@ -27384,7 +27386,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="501" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
         <v>801</v>
       </c>
@@ -27431,7 +27433,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="502" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
         <v>801</v>
       </c>
@@ -27478,7 +27480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="503" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
         <v>801</v>
       </c>
@@ -27525,7 +27527,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="504" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="2" t="s">
         <v>801</v>
       </c>
@@ -27572,7 +27574,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="505" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
         <v>801</v>
       </c>
@@ -27619,7 +27621,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="506" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="2" t="s">
         <v>801</v>
       </c>
@@ -27666,7 +27668,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="507" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
         <v>801</v>
       </c>
@@ -27713,7 +27715,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="508" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="2" t="s">
         <v>801</v>
       </c>
@@ -27760,7 +27762,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="509" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="2" t="s">
         <v>801</v>
       </c>
@@ -27807,7 +27809,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="510" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="2" t="s">
         <v>801</v>
       </c>
@@ -27854,7 +27856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="511" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="2" t="s">
         <v>807</v>
       </c>
@@ -27904,7 +27906,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="512" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
         <v>801</v>
       </c>
@@ -27951,7 +27953,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="513" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
         <v>801</v>
       </c>
@@ -27998,7 +28000,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="514" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
         <v>801</v>
       </c>
@@ -28045,7 +28047,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="515" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
         <v>801</v>
       </c>
@@ -28092,7 +28094,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="516" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="2" t="s">
         <v>801</v>
       </c>
@@ -28139,7 +28141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="517" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
         <v>801</v>
       </c>
@@ -28186,7 +28188,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="518" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="5" t="s">
         <v>807</v>
       </c>
@@ -28236,7 +28238,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="519" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
         <v>801</v>
       </c>
@@ -28283,7 +28285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
         <v>802</v>
       </c>
@@ -28333,7 +28335,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="521" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
         <v>801</v>
       </c>
@@ -28380,7 +28382,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="522" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
         <v>801</v>
       </c>
@@ -28427,7 +28429,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="523" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
         <v>801</v>
       </c>
@@ -28474,7 +28476,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="524" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
         <v>801</v>
       </c>
@@ -28521,7 +28523,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="525" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
         <v>801</v>
       </c>
@@ -28568,7 +28570,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="11" t="s">
         <v>813</v>
       </c>
@@ -28615,7 +28617,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="11" t="s">
         <v>813</v>
       </c>
@@ -28662,7 +28664,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="11" t="s">
         <v>813</v>
       </c>
@@ -28709,7 +28711,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="11" t="s">
         <v>813</v>
       </c>
@@ -28756,7 +28758,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="11" t="s">
         <v>813</v>
       </c>
@@ -28803,7 +28805,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="11" t="s">
         <v>813</v>
       </c>
@@ -28850,7 +28852,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="532" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
         <v>813</v>
       </c>
@@ -28897,7 +28899,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="11" t="s">
         <v>813</v>
       </c>
@@ -28944,7 +28946,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="11" t="s">
         <v>813</v>
       </c>
@@ -28991,7 +28993,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="11" t="s">
         <v>813</v>
       </c>
@@ -29038,7 +29040,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="11" t="s">
         <v>813</v>
       </c>
@@ -29085,7 +29087,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="11" t="s">
         <v>813</v>
       </c>
@@ -29132,7 +29134,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="11" t="s">
         <v>813</v>
       </c>
@@ -29179,7 +29181,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="11" t="s">
         <v>813</v>
       </c>
@@ -29226,7 +29228,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="11" t="s">
         <v>813</v>
       </c>
@@ -29273,7 +29275,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="11" t="s">
         <v>813</v>
       </c>
@@ -29320,7 +29322,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="11" t="s">
         <v>813</v>
       </c>
@@ -29367,7 +29369,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="11" t="s">
         <v>813</v>
       </c>
@@ -29414,7 +29416,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="11" t="s">
         <v>813</v>
       </c>
@@ -29461,7 +29463,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="11" t="s">
         <v>813</v>
       </c>
@@ -29508,7 +29510,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="11" t="s">
         <v>813</v>
       </c>
@@ -29555,7 +29557,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="11" t="s">
         <v>813</v>
       </c>
@@ -29602,7 +29604,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="11" t="s">
         <v>813</v>
       </c>
@@ -29649,7 +29651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="11" t="s">
         <v>813</v>
       </c>
@@ -29696,7 +29698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="11" t="s">
         <v>813</v>
       </c>
@@ -29743,7 +29745,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="11" t="s">
         <v>813</v>
       </c>
@@ -29790,7 +29792,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="11" t="s">
         <v>813</v>
       </c>
@@ -29837,7 +29839,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="553" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:16" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="6" t="s">
         <v>801</v>
       </c>
@@ -29884,7 +29886,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="554" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:16" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="6" t="s">
         <v>801</v>
       </c>
@@ -29931,7 +29933,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="11" t="s">
         <v>813</v>
       </c>
@@ -29978,7 +29980,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="11" t="s">
         <v>813</v>
       </c>
@@ -30025,7 +30027,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="11" t="s">
         <v>813</v>
       </c>
@@ -30072,7 +30074,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="11" t="s">
         <v>813</v>
       </c>
@@ -30119,7 +30121,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="11" t="s">
         <v>813</v>
       </c>
@@ -30166,7 +30168,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="560" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:16" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="6" t="s">
         <v>801</v>
       </c>
@@ -30213,7 +30215,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="11" t="s">
         <v>813</v>
       </c>
@@ -30260,7 +30262,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="562" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:16" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="6" t="s">
         <v>801</v>
       </c>
@@ -30307,7 +30309,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="11" t="s">
         <v>813</v>
       </c>
@@ -30354,7 +30356,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="11" t="s">
         <v>813</v>
       </c>
@@ -30401,7 +30403,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="11" t="s">
         <v>813</v>
       </c>
@@ -30448,7 +30450,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="11" t="s">
         <v>813</v>
       </c>
@@ -30495,7 +30497,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="11" t="s">
         <v>813</v>
       </c>
@@ -30542,7 +30544,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="11" t="s">
         <v>813</v>
       </c>
@@ -30589,7 +30591,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="11" t="s">
         <v>813</v>
       </c>
@@ -30636,7 +30638,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="11" t="s">
         <v>813</v>
       </c>
@@ -30683,7 +30685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="11" t="s">
         <v>813</v>
       </c>
@@ -30730,7 +30732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="11" t="s">
         <v>813</v>
       </c>
@@ -30777,7 +30779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="11" t="s">
         <v>813</v>
       </c>
@@ -30824,7 +30826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="11" t="s">
         <v>813</v>
       </c>
@@ -30871,7 +30873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="11" t="s">
         <v>813</v>
       </c>
@@ -30918,7 +30920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="11" t="s">
         <v>813</v>
       </c>
@@ -30965,7 +30967,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="11" t="s">
         <v>813</v>
       </c>
@@ -31012,7 +31014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="11" t="s">
         <v>813</v>
       </c>
@@ -31059,7 +31061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="11" t="s">
         <v>813</v>
       </c>
@@ -31106,7 +31108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="11" t="s">
         <v>813</v>
       </c>
@@ -31153,7 +31155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="11" t="s">
         <v>813</v>
       </c>
@@ -31200,7 +31202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="11" t="s">
         <v>813</v>
       </c>
@@ -31247,7 +31249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="583" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
         <v>801</v>
       </c>
@@ -31294,7 +31296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="11" t="s">
         <v>813</v>
       </c>
@@ -31341,7 +31343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="11" t="s">
         <v>813</v>
       </c>
@@ -31388,7 +31390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="11" t="s">
         <v>813</v>
       </c>
@@ -31435,7 +31437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="11" t="s">
         <v>813</v>
       </c>
@@ -31482,7 +31484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="588" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
         <v>801</v>
       </c>
@@ -31529,7 +31531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="11" t="s">
         <v>813</v>
       </c>
@@ -31576,7 +31578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="11" t="s">
         <v>813</v>
       </c>
@@ -31623,7 +31625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="591" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:16" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
         <v>801</v>
       </c>
@@ -31670,7 +31672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="11" t="s">
         <v>813</v>
       </c>
@@ -31717,7 +31719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="11" t="s">
         <v>813</v>
       </c>
@@ -31764,7 +31766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="11" t="s">
         <v>813</v>
       </c>
@@ -31811,7 +31813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="11" t="s">
         <v>813</v>
       </c>
@@ -31858,7 +31860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="11" t="s">
         <v>813</v>
       </c>
@@ -31905,7 +31907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="11" t="s">
         <v>813</v>
       </c>
@@ -31952,7 +31954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="11" t="s">
         <v>813</v>
       </c>
@@ -31999,7 +32001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="11" t="s">
         <v>813</v>
       </c>
@@ -32046,7 +32048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="11" t="s">
         <v>813</v>
       </c>
@@ -32093,7 +32095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="11" t="s">
         <v>813</v>
       </c>
@@ -32140,7 +32142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="11" t="s">
         <v>813</v>
       </c>
@@ -32187,7 +32189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="11" t="s">
         <v>813</v>
       </c>
@@ -32234,7 +32236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="11" t="s">
         <v>813</v>
       </c>
@@ -32281,7 +32283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="11" t="s">
         <v>813</v>
       </c>
@@ -32328,7 +32330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="11" t="s">
         <v>813</v>
       </c>
@@ -32376,8 +32378,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P606"/>
-  <sortState ref="C2:P606">
+  <autoFilter ref="A1:P606" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="14">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:P606">
     <sortCondition ref="C8:C606"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32387,69 +32395,69 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.09765625" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>798</v>
       </c>
